--- a/reports/一级子公司A_现金流量表_2025-07.xlsx
+++ b/reports/一级子公司A_现金流量表_2025-07.xlsx
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>165984000</v>
+        <v>166428817</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>1028508000</v>
+        <v>1028807520</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>3350623</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>20783138</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>1676609</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>10393682</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>840322</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>5197241</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>668679</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>4156341</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>505386</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>3119078</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>333815</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>2077809</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>252843</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>1559687</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>166980</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>1038897</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>420809</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>2599261</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>210272</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>1305497</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>133415</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>826242</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>425600</v>
+        <v>426002</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>2637200</v>
+        <v>2637238</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>3024000</v>
+        <v>3016555</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>18738000</v>
+        <v>18735116</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>169433600</v>
+        <v>178431127</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>107520000</v>
+        <v>107973199</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>666240000</v>
+        <v>666508832</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>1114700</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>6926635</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>840107</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>5197790</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>559024</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>3464164</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>418716</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>2598177</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>280366</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>1732566</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>209885</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>1305422</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>17584000</v>
+        <v>17667988</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>108958000</v>
+        <v>109001011</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2841,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>8960000</v>
+        <v>8915213</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>55520000</v>
+        <v>55495785</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>3696000</v>
+        <v>3713364</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>22902000</v>
+        <v>22911894</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>137760000</v>
+        <v>141692562</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>31673600</v>
+        <v>36738565</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3093,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>180000</v>
+        <v>180781</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>1260000</v>
+        <v>1260531</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>1500000</v>
+        <v>1507436</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>10500000</v>
+        <v>10504447</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>920000</v>
+        <v>915869</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>6440000</v>
+        <v>6437708</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>1680000</v>
+        <v>1688217</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>14000000</v>
+        <v>13968567</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>98000000</v>
+        <v>97988175</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2000000</v>
+        <v>2001405</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>14000000</v>
+        <v>13999681</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>10000000</v>
+        <v>10009142</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>70000000</v>
+        <v>70011477</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3454,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>380000</v>
+        <v>381893</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>2660000</v>
+        <v>2661181</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>14380000</v>
+        <v>14350460</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-12700000</v>
+        <v>-12662243</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>3500000</v>
+        <v>3506157</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>24500000</v>
+        <v>24501825</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>5500000</v>
+        <v>5492135</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>38500000</v>
+        <v>38492028</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>5500000</v>
+        <v>5515862</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>38500000</v>
+        <v>38512414</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>180000</v>
+        <v>179273</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>1260000</v>
+        <v>1259490</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>9180000</v>
+        <v>9177565</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>4500000</v>
+        <v>4477504</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>31500000</v>
+        <v>31486244</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>4500000</v>
+        <v>4521188</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>31500000</v>
+        <v>31512100</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>720000</v>
+        <v>717174</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>5040000</v>
+        <v>5038534</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>630000</v>
+        <v>629210</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>4410000</v>
+        <v>4409880</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3935,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>90000</v>
+        <v>89968</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>630000</v>
+        <v>629927</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>5310000</v>
+        <v>5284646</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>3870000</v>
+        <v>3892919</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>22843600</v>
+        <v>27969241</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>22843600</v>
+        <v>27969241</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
